--- a/artfynd/A 46375-2025 artfynd.xlsx
+++ b/artfynd/A 46375-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1158,6 +1158,3348 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>133828543</v>
+      </c>
+      <c r="B7" t="n">
+        <v>83315</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Linnbäckrönningen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>514387</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6910548</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>16:51</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>16:51</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>133828532</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79333</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Linnbäckrönningen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>514353</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6910600</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>133828555</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57958</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Linnbäckrönningen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>514481</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6910474</v>
+      </c>
+      <c r="S9" t="n">
+        <v>6</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>133828569</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57958</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Linnbäckrönningen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>514390</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6910444</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>17:59</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>17:59</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>133828560</v>
+      </c>
+      <c r="B11" t="n">
+        <v>83315</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Linnbäckrönningen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>514463</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6910442</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>17:28</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>17:28</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>133828547</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79333</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Linnbäckrönningen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>514367</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6910512</v>
+      </c>
+      <c r="S12" t="n">
+        <v>6</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>17:04</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>17:04</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>133828553</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57958</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Linnbäckrönningen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>514473</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6910487</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>133828533</v>
+      </c>
+      <c r="B14" t="n">
+        <v>83315</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Linnbäckrönningen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>514356</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6910600</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>133828530</v>
+      </c>
+      <c r="B15" t="n">
+        <v>80438</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Linnbäckrönningen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>514326</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6910602</v>
+      </c>
+      <c r="S15" t="n">
+        <v>6</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>133828540</v>
+      </c>
+      <c r="B16" t="n">
+        <v>83315</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Linnbäckrönningen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>514417</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6910549</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>16:47</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>16:47</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>133828557</v>
+      </c>
+      <c r="B17" t="n">
+        <v>83315</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Linnbäckrönningen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>514473</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6910454</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>133828551</v>
+      </c>
+      <c r="B18" t="n">
+        <v>83307</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>308</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Brunpudrad nållav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Linnbäckrönningen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>514417</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6910512</v>
+      </c>
+      <c r="S18" t="n">
+        <v>7</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>17:16</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>17:16</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>133828539</v>
+      </c>
+      <c r="B19" t="n">
+        <v>83315</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Linnbäckrönningen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>514389</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6910577</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>16:42</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>16:42</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>133828558</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57958</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Linnbäckrönningen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>514472</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6910452</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>17:26</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>17:26</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>133828546</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99130</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Linnbäckrönningen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>514353</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6910523</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>17:01</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>17:01</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>4 ex</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>133828570</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79333</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Linnbäckrönningen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>514315</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6910507</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>18:06</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>18:06</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>133828548</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99130</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Linnbäckrönningen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>514370</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6910494</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>17:07</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>17:07</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>25 ex</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>133828549</v>
+      </c>
+      <c r="B24" t="n">
+        <v>83298</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6439</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Gulnål</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Linnbäckrönningen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>514401</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6910501</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>17:09</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>17:09</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>133828559</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57958</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Linnbäckrönningen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>514468</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6910453</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>17:27</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>17:27</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>133828556</v>
+      </c>
+      <c r="B26" t="n">
+        <v>83315</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Linnbäckrönningen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>514478</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6910471</v>
+      </c>
+      <c r="S26" t="n">
+        <v>6</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>17:24</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>17:24</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>133828542</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57958</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Linnbäckrönningen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>514396</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6910543</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på granhögstubbe</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>133828545</v>
+      </c>
+      <c r="B28" t="n">
+        <v>91918</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Linnbäckrönningen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>514388</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6910542</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>16:52</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>16:52</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>133828550</v>
+      </c>
+      <c r="B29" t="n">
+        <v>83315</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Linnbäckrönningen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>514408</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6910507</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>17:11</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>17:11</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>133828535</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57958</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Linnbäckrönningen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>514363</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6910589</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>133828552</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57958</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Linnbäckrönningen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>514420</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6910512</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>17:17</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>17:17</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>133828544</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79333</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Linnbäckrönningen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>514389</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6910544</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>16:51</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>16:51</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>133828538</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57955</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Linnbäckrönningen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>514383</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6910570</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>133828531</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79357</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Linnbäckrönningen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>514336</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6910600</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>16:29</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>16:29</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>133828536</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79333</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Linnbäckrönningen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>514362</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6910579</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>16:37</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>16:37</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>133828537</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57958</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Linnbäckrönningen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>514367</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6910574</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 46375-2025 artfynd.xlsx
+++ b/artfynd/A 46375-2025 artfynd.xlsx
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133828543</v>
+        <v>133828532</v>
       </c>
       <c r="B7" t="n">
-        <v>83315</v>
+        <v>79334</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>514387</v>
+        <v>514353</v>
       </c>
       <c r="R7" t="n">
-        <v>6910548</v>
+        <v>6910600</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1230,7 +1230,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1267,10 +1267,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133828532</v>
+        <v>133828543</v>
       </c>
       <c r="B8" t="n">
-        <v>79333</v>
+        <v>83316</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1278,21 +1278,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>514353</v>
+        <v>514387</v>
       </c>
       <c r="R8" t="n">
-        <v>6910600</v>
+        <v>6910548</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1374,7 +1374,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133828555</v>
+        <v>133828569</v>
       </c>
       <c r="B9" t="n">
         <v>57958</v>
@@ -1417,13 +1417,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>514481</v>
+        <v>514390</v>
       </c>
       <c r="R9" t="n">
-        <v>6910474</v>
+        <v>6910444</v>
       </c>
       <c r="S9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1494,7 +1494,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133828569</v>
+        <v>133828555</v>
       </c>
       <c r="B10" t="n">
         <v>57958</v>
@@ -1537,13 +1537,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>514390</v>
+        <v>514481</v>
       </c>
       <c r="R10" t="n">
-        <v>6910444</v>
+        <v>6910474</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1617,7 +1617,7 @@
         <v>133828560</v>
       </c>
       <c r="B11" t="n">
-        <v>83315</v>
+        <v>83316</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1724,7 +1724,7 @@
         <v>133828547</v>
       </c>
       <c r="B12" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1948,10 +1948,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133828533</v>
+        <v>133828551</v>
       </c>
       <c r="B14" t="n">
-        <v>83315</v>
+        <v>83308</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1959,21 +1959,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>308</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>514356</v>
+        <v>514417</v>
       </c>
       <c r="R14" t="n">
-        <v>6910600</v>
+        <v>6910512</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2055,10 +2055,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133828530</v>
+        <v>133828540</v>
       </c>
       <c r="B15" t="n">
-        <v>80438</v>
+        <v>83316</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2066,21 +2066,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2090,13 +2090,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>514326</v>
+        <v>514417</v>
       </c>
       <c r="R15" t="n">
-        <v>6910602</v>
+        <v>6910549</v>
       </c>
       <c r="S15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2162,10 +2162,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133828540</v>
+        <v>133828530</v>
       </c>
       <c r="B16" t="n">
-        <v>83315</v>
+        <v>80439</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2173,21 +2173,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2197,13 +2197,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>514417</v>
+        <v>514326</v>
       </c>
       <c r="R16" t="n">
-        <v>6910549</v>
+        <v>6910602</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2242,7 +2242,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2272,7 +2272,7 @@
         <v>133828557</v>
       </c>
       <c r="B17" t="n">
-        <v>83315</v>
+        <v>83316</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2376,10 +2376,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133828551</v>
+        <v>133828533</v>
       </c>
       <c r="B18" t="n">
-        <v>83307</v>
+        <v>83316</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2387,21 +2387,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>308</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2411,13 +2411,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>514417</v>
+        <v>514356</v>
       </c>
       <c r="R18" t="n">
-        <v>6910512</v>
+        <v>6910600</v>
       </c>
       <c r="S18" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2486,7 +2486,7 @@
         <v>133828539</v>
       </c>
       <c r="B19" t="n">
-        <v>83315</v>
+        <v>83316</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         <v>133828546</v>
       </c>
       <c r="B21" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>133828570</v>
       </c>
       <c r="B22" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2929,32 +2929,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133828548</v>
+        <v>133828549</v>
       </c>
       <c r="B23" t="n">
-        <v>99130</v>
+        <v>83299</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6439</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2964,10 +2964,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>514370</v>
+        <v>514401</v>
       </c>
       <c r="R23" t="n">
-        <v>6910494</v>
+        <v>6910501</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2999,7 +2999,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3009,12 +3009,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:07</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>25 ex</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3041,45 +3036,53 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133828549</v>
+        <v>133828559</v>
       </c>
       <c r="B24" t="n">
-        <v>83298</v>
+        <v>57958</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6439</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Linnbäckrönningen, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>514401</v>
+        <v>514468</v>
       </c>
       <c r="R24" t="n">
-        <v>6910501</v>
+        <v>6910453</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3111,7 +3114,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3121,7 +3124,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>17:27</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3148,53 +3156,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133828559</v>
+        <v>133828548</v>
       </c>
       <c r="B25" t="n">
-        <v>57958</v>
+        <v>99132</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Linnbäckrönningen, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>514468</v>
+        <v>514370</v>
       </c>
       <c r="R25" t="n">
-        <v>6910453</v>
+        <v>6910494</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3236,12 +3236,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>25 ex</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3271,7 +3271,7 @@
         <v>133828556</v>
       </c>
       <c r="B26" t="n">
-        <v>83315</v>
+        <v>83316</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3498,7 +3498,7 @@
         <v>133828545</v>
       </c>
       <c r="B28" t="n">
-        <v>91918</v>
+        <v>91920</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         <v>133828550</v>
       </c>
       <c r="B29" t="n">
-        <v>83315</v>
+        <v>83316</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3952,7 +3952,7 @@
         <v>133828544</v>
       </c>
       <c r="B32" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4171,7 +4171,7 @@
         <v>133828531</v>
       </c>
       <c r="B34" t="n">
-        <v>79357</v>
+        <v>79358</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
         <v>133828536</v>
       </c>
       <c r="B35" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 46375-2025 artfynd.xlsx
+++ b/artfynd/A 46375-2025 artfynd.xlsx
@@ -1828,10 +1828,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133828553</v>
+        <v>133828540</v>
       </c>
       <c r="B13" t="n">
-        <v>57958</v>
+        <v>83316</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1839,42 +1839,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Linnbäckrönningen, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>514473</v>
+        <v>514417</v>
       </c>
       <c r="R13" t="n">
-        <v>6910487</v>
+        <v>6910549</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1906,7 +1898,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1916,12 +1908,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:21</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1948,10 +1935,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133828551</v>
+        <v>133828530</v>
       </c>
       <c r="B14" t="n">
-        <v>83308</v>
+        <v>80439</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1959,21 +1946,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>308</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1983,13 +1970,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>514417</v>
+        <v>514326</v>
       </c>
       <c r="R14" t="n">
-        <v>6910512</v>
+        <v>6910602</v>
       </c>
       <c r="S14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2018,7 +2005,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2028,7 +2015,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2055,7 +2042,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133828540</v>
+        <v>133828557</v>
       </c>
       <c r="B15" t="n">
         <v>83316</v>
@@ -2090,10 +2077,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>514417</v>
+        <v>514473</v>
       </c>
       <c r="R15" t="n">
-        <v>6910549</v>
+        <v>6910454</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2125,7 +2112,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2135,7 +2122,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2162,10 +2149,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133828530</v>
+        <v>133828533</v>
       </c>
       <c r="B16" t="n">
-        <v>80439</v>
+        <v>83316</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2173,21 +2160,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2197,13 +2184,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>514326</v>
+        <v>514356</v>
       </c>
       <c r="R16" t="n">
-        <v>6910602</v>
+        <v>6910600</v>
       </c>
       <c r="S16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2232,7 +2219,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2242,7 +2229,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2269,10 +2256,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133828557</v>
+        <v>133828551</v>
       </c>
       <c r="B17" t="n">
-        <v>83316</v>
+        <v>83308</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2280,21 +2267,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6440</v>
+        <v>308</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2304,13 +2291,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>514473</v>
+        <v>514417</v>
       </c>
       <c r="R17" t="n">
-        <v>6910454</v>
+        <v>6910512</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2339,7 +2326,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2349,7 +2336,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2376,10 +2363,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133828533</v>
+        <v>133828553</v>
       </c>
       <c r="B18" t="n">
-        <v>83316</v>
+        <v>57958</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2387,34 +2374,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Linnbäckrönningen, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>514356</v>
+        <v>514473</v>
       </c>
       <c r="R18" t="n">
-        <v>6910600</v>
+        <v>6910487</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2446,7 +2441,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2456,7 +2451,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3709,10 +3709,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133828535</v>
+        <v>133828544</v>
       </c>
       <c r="B30" t="n">
-        <v>57958</v>
+        <v>79334</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3720,42 +3720,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Linnbäckrönningen, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>514363</v>
+        <v>514389</v>
       </c>
       <c r="R30" t="n">
-        <v>6910589</v>
+        <v>6910544</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3787,7 +3779,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3797,12 +3789,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:36</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3829,7 +3816,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133828552</v>
+        <v>133828535</v>
       </c>
       <c r="B31" t="n">
         <v>57958</v>
@@ -3872,10 +3859,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>514420</v>
+        <v>514363</v>
       </c>
       <c r="R31" t="n">
-        <v>6910512</v>
+        <v>6910589</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3907,7 +3894,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3917,7 +3904,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -3949,10 +3936,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133828544</v>
+        <v>133828552</v>
       </c>
       <c r="B32" t="n">
-        <v>79334</v>
+        <v>57958</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3960,34 +3947,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Linnbäckrönningen, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>514389</v>
+        <v>514420</v>
       </c>
       <c r="R32" t="n">
-        <v>6910544</v>
+        <v>6910512</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4019,7 +4014,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4029,7 +4024,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:17</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 46375-2025 artfynd.xlsx
+++ b/artfynd/A 46375-2025 artfynd.xlsx
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133828532</v>
+        <v>133828543</v>
       </c>
       <c r="B7" t="n">
-        <v>79334</v>
+        <v>83318</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>514353</v>
+        <v>514387</v>
       </c>
       <c r="R7" t="n">
-        <v>6910600</v>
+        <v>6910548</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1230,7 +1230,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1267,10 +1267,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133828543</v>
+        <v>133828532</v>
       </c>
       <c r="B8" t="n">
-        <v>83316</v>
+        <v>79334</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1278,21 +1278,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>514387</v>
+        <v>514353</v>
       </c>
       <c r="R8" t="n">
-        <v>6910548</v>
+        <v>6910600</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1617,7 +1617,7 @@
         <v>133828560</v>
       </c>
       <c r="B11" t="n">
-        <v>83316</v>
+        <v>83318</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1828,10 +1828,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133828540</v>
+        <v>133828551</v>
       </c>
       <c r="B13" t="n">
-        <v>83316</v>
+        <v>83310</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1839,21 +1839,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>308</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1866,10 +1866,10 @@
         <v>514417</v>
       </c>
       <c r="R13" t="n">
-        <v>6910549</v>
+        <v>6910512</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1908,7 +1908,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1935,10 +1935,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133828530</v>
+        <v>133828540</v>
       </c>
       <c r="B14" t="n">
-        <v>80439</v>
+        <v>83318</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1946,21 +1946,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1970,13 +1970,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>514326</v>
+        <v>514417</v>
       </c>
       <c r="R14" t="n">
-        <v>6910602</v>
+        <v>6910549</v>
       </c>
       <c r="S14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2005,7 +2005,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2015,7 +2015,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2045,7 +2045,7 @@
         <v>133828557</v>
       </c>
       <c r="B15" t="n">
-        <v>83316</v>
+        <v>83318</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>133828533</v>
       </c>
       <c r="B16" t="n">
-        <v>83316</v>
+        <v>83318</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2256,10 +2256,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133828551</v>
+        <v>133828530</v>
       </c>
       <c r="B17" t="n">
-        <v>83308</v>
+        <v>80439</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2267,21 +2267,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>308</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2291,13 +2291,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>514417</v>
+        <v>514326</v>
       </c>
       <c r="R17" t="n">
-        <v>6910512</v>
+        <v>6910602</v>
       </c>
       <c r="S17" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2326,7 +2326,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2336,7 +2336,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2486,7 +2486,7 @@
         <v>133828539</v>
       </c>
       <c r="B19" t="n">
-        <v>83316</v>
+        <v>83318</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         <v>133828546</v>
       </c>
       <c r="B21" t="n">
-        <v>99132</v>
+        <v>99138</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>133828549</v>
       </c>
       <c r="B23" t="n">
-        <v>83299</v>
+        <v>83301</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>133828548</v>
       </c>
       <c r="B25" t="n">
-        <v>99132</v>
+        <v>99138</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3271,7 +3271,7 @@
         <v>133828556</v>
       </c>
       <c r="B26" t="n">
-        <v>83316</v>
+        <v>83318</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3498,7 +3498,7 @@
         <v>133828545</v>
       </c>
       <c r="B28" t="n">
-        <v>91920</v>
+        <v>91926</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3602,10 +3602,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133828550</v>
+        <v>133828544</v>
       </c>
       <c r="B29" t="n">
-        <v>83316</v>
+        <v>79334</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3613,21 +3613,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3637,10 +3637,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>514408</v>
+        <v>514389</v>
       </c>
       <c r="R29" t="n">
-        <v>6910507</v>
+        <v>6910544</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3672,7 +3672,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3682,7 +3682,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3709,10 +3709,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133828544</v>
+        <v>133828550</v>
       </c>
       <c r="B30" t="n">
-        <v>79334</v>
+        <v>83318</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3720,21 +3720,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3744,10 +3744,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>514389</v>
+        <v>514408</v>
       </c>
       <c r="R30" t="n">
-        <v>6910544</v>
+        <v>6910507</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3779,7 +3779,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3789,7 +3789,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 46375-2025 artfynd.xlsx
+++ b/artfynd/A 46375-2025 artfynd.xlsx
@@ -1163,7 +1163,7 @@
         <v>133828543</v>
       </c>
       <c r="B7" t="n">
-        <v>83318</v>
+        <v>83319</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1617,7 +1617,7 @@
         <v>133828560</v>
       </c>
       <c r="B11" t="n">
-        <v>83318</v>
+        <v>83319</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         <v>133828551</v>
       </c>
       <c r="B13" t="n">
-        <v>83310</v>
+        <v>83311</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
         <v>133828540</v>
       </c>
       <c r="B14" t="n">
-        <v>83318</v>
+        <v>83319</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2042,10 +2042,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133828557</v>
+        <v>133828530</v>
       </c>
       <c r="B15" t="n">
-        <v>83318</v>
+        <v>80439</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2053,21 +2053,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2077,13 +2077,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>514473</v>
+        <v>514326</v>
       </c>
       <c r="R15" t="n">
-        <v>6910454</v>
+        <v>6910602</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2149,10 +2149,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133828533</v>
+        <v>133828557</v>
       </c>
       <c r="B16" t="n">
-        <v>83318</v>
+        <v>83319</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2184,10 +2184,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>514356</v>
+        <v>514473</v>
       </c>
       <c r="R16" t="n">
-        <v>6910600</v>
+        <v>6910454</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2219,7 +2219,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2256,10 +2256,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133828530</v>
+        <v>133828533</v>
       </c>
       <c r="B17" t="n">
-        <v>80439</v>
+        <v>83319</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2267,21 +2267,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2291,13 +2291,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>514326</v>
+        <v>514356</v>
       </c>
       <c r="R17" t="n">
-        <v>6910602</v>
+        <v>6910600</v>
       </c>
       <c r="S17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2326,7 +2326,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2336,7 +2336,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2486,7 +2486,7 @@
         <v>133828539</v>
       </c>
       <c r="B19" t="n">
-        <v>83318</v>
+        <v>83319</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         <v>133828546</v>
       </c>
       <c r="B21" t="n">
-        <v>99138</v>
+        <v>99140</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2929,45 +2929,53 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133828549</v>
+        <v>133828559</v>
       </c>
       <c r="B23" t="n">
-        <v>83301</v>
+        <v>57958</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6439</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Linnbäckrönningen, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>514401</v>
+        <v>514468</v>
       </c>
       <c r="R23" t="n">
-        <v>6910501</v>
+        <v>6910453</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2999,7 +3007,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3009,7 +3017,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>17:27</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3036,53 +3049,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133828559</v>
+        <v>133828549</v>
       </c>
       <c r="B24" t="n">
-        <v>57958</v>
+        <v>83302</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6439</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Linnbäckrönningen, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>514468</v>
+        <v>514401</v>
       </c>
       <c r="R24" t="n">
-        <v>6910453</v>
+        <v>6910501</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3114,7 +3119,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3124,12 +3129,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:27</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3159,7 +3159,7 @@
         <v>133828548</v>
       </c>
       <c r="B25" t="n">
-        <v>99138</v>
+        <v>99140</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3271,7 +3271,7 @@
         <v>133828556</v>
       </c>
       <c r="B26" t="n">
-        <v>83318</v>
+        <v>83319</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3498,7 +3498,7 @@
         <v>133828545</v>
       </c>
       <c r="B28" t="n">
-        <v>91926</v>
+        <v>91928</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3602,10 +3602,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133828544</v>
+        <v>133828535</v>
       </c>
       <c r="B29" t="n">
-        <v>79334</v>
+        <v>57958</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3613,34 +3613,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Linnbäckrönningen, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>514389</v>
+        <v>514363</v>
       </c>
       <c r="R29" t="n">
-        <v>6910544</v>
+        <v>6910589</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3672,7 +3680,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3682,7 +3690,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3709,10 +3722,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133828550</v>
+        <v>133828552</v>
       </c>
       <c r="B30" t="n">
-        <v>83318</v>
+        <v>57958</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3720,34 +3733,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Linnbäckrönningen, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>514408</v>
+        <v>514420</v>
       </c>
       <c r="R30" t="n">
-        <v>6910507</v>
+        <v>6910512</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3779,7 +3800,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3789,7 +3810,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:17</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3816,10 +3842,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133828535</v>
+        <v>133828544</v>
       </c>
       <c r="B31" t="n">
-        <v>57958</v>
+        <v>79334</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3827,42 +3853,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Linnbäckrönningen, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>514363</v>
+        <v>514389</v>
       </c>
       <c r="R31" t="n">
-        <v>6910589</v>
+        <v>6910544</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3894,7 +3912,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3904,12 +3922,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:36</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3936,10 +3949,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133828552</v>
+        <v>133828550</v>
       </c>
       <c r="B32" t="n">
-        <v>57958</v>
+        <v>83319</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3947,42 +3960,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Linnbäckrönningen, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>514420</v>
+        <v>514408</v>
       </c>
       <c r="R32" t="n">
-        <v>6910512</v>
+        <v>6910507</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4014,7 +4019,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4024,12 +4029,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>17:17</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 46375-2025 artfynd.xlsx
+++ b/artfynd/A 46375-2025 artfynd.xlsx
@@ -2929,53 +2929,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133828559</v>
+        <v>133828549</v>
       </c>
       <c r="B23" t="n">
-        <v>57958</v>
+        <v>83302</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6439</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Linnbäckrönningen, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>514468</v>
+        <v>514401</v>
       </c>
       <c r="R23" t="n">
-        <v>6910453</v>
+        <v>6910501</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3007,7 +2999,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3017,12 +3009,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:27</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3049,45 +3036,53 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133828549</v>
+        <v>133828559</v>
       </c>
       <c r="B24" t="n">
-        <v>83302</v>
+        <v>57958</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6439</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Linnbäckrönningen, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>514401</v>
+        <v>514468</v>
       </c>
       <c r="R24" t="n">
-        <v>6910501</v>
+        <v>6910453</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3119,7 +3114,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3129,7 +3124,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>17:27</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3602,10 +3602,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133828535</v>
+        <v>133828544</v>
       </c>
       <c r="B29" t="n">
-        <v>57958</v>
+        <v>79334</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3613,42 +3613,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Linnbäckrönningen, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>514363</v>
+        <v>514389</v>
       </c>
       <c r="R29" t="n">
-        <v>6910589</v>
+        <v>6910544</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3680,7 +3672,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3690,12 +3682,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:36</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3722,10 +3709,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133828552</v>
+        <v>133828550</v>
       </c>
       <c r="B30" t="n">
-        <v>57958</v>
+        <v>83319</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3733,42 +3720,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Linnbäckrönningen, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>514420</v>
+        <v>514408</v>
       </c>
       <c r="R30" t="n">
-        <v>6910512</v>
+        <v>6910507</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3800,7 +3779,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3810,12 +3789,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:17</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3842,10 +3816,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133828544</v>
+        <v>133828535</v>
       </c>
       <c r="B31" t="n">
-        <v>79334</v>
+        <v>57958</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3853,34 +3827,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Linnbäckrönningen, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>514389</v>
+        <v>514363</v>
       </c>
       <c r="R31" t="n">
-        <v>6910544</v>
+        <v>6910589</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3912,7 +3894,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3922,7 +3904,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3949,10 +3936,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133828550</v>
+        <v>133828552</v>
       </c>
       <c r="B32" t="n">
-        <v>83319</v>
+        <v>57958</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3960,34 +3947,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Linnbäckrönningen, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>514408</v>
+        <v>514420</v>
       </c>
       <c r="R32" t="n">
-        <v>6910507</v>
+        <v>6910512</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4019,7 +4014,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4029,7 +4024,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:17</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 46375-2025 artfynd.xlsx
+++ b/artfynd/A 46375-2025 artfynd.xlsx
@@ -2483,10 +2483,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133828539</v>
+        <v>133828558</v>
       </c>
       <c r="B19" t="n">
-        <v>83319</v>
+        <v>57958</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2494,34 +2494,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Linnbäckrönningen, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>514389</v>
+        <v>514472</v>
       </c>
       <c r="R19" t="n">
-        <v>6910577</v>
+        <v>6910452</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2553,7 +2561,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2563,7 +2571,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:26</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2590,10 +2603,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133828558</v>
+        <v>133828539</v>
       </c>
       <c r="B20" t="n">
-        <v>57958</v>
+        <v>83319</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2601,42 +2614,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Linnbäckrönningen, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>514472</v>
+        <v>514389</v>
       </c>
       <c r="R20" t="n">
-        <v>6910452</v>
+        <v>6910577</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2668,7 +2673,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2678,12 +2683,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:26</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 46375-2025 artfynd.xlsx
+++ b/artfynd/A 46375-2025 artfynd.xlsx
@@ -2483,10 +2483,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133828558</v>
+        <v>133828539</v>
       </c>
       <c r="B19" t="n">
-        <v>57958</v>
+        <v>83319</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2494,42 +2494,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Linnbäckrönningen, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>514472</v>
+        <v>514389</v>
       </c>
       <c r="R19" t="n">
-        <v>6910452</v>
+        <v>6910577</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2561,7 +2553,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2571,12 +2563,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:26</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2603,10 +2590,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133828539</v>
+        <v>133828558</v>
       </c>
       <c r="B20" t="n">
-        <v>83319</v>
+        <v>57958</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2614,34 +2601,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Linnbäckrönningen, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>514389</v>
+        <v>514472</v>
       </c>
       <c r="R20" t="n">
-        <v>6910577</v>
+        <v>6910452</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2673,7 +2668,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2683,7 +2678,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:26</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 46375-2025 artfynd.xlsx
+++ b/artfynd/A 46375-2025 artfynd.xlsx
@@ -1163,7 +1163,7 @@
         <v>133828543</v>
       </c>
       <c r="B7" t="n">
-        <v>83319</v>
+        <v>83333</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>133828532</v>
       </c>
       <c r="B8" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>133828569</v>
       </c>
       <c r="B9" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1497,7 +1497,7 @@
         <v>133828555</v>
       </c>
       <c r="B10" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1617,7 +1617,7 @@
         <v>133828560</v>
       </c>
       <c r="B11" t="n">
-        <v>83319</v>
+        <v>83333</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1724,7 +1724,7 @@
         <v>133828547</v>
       </c>
       <c r="B12" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1828,10 +1828,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133828551</v>
+        <v>133828540</v>
       </c>
       <c r="B13" t="n">
-        <v>83311</v>
+        <v>83333</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1839,21 +1839,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>308</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1866,10 +1866,10 @@
         <v>514417</v>
       </c>
       <c r="R13" t="n">
-        <v>6910512</v>
+        <v>6910549</v>
       </c>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1908,7 +1908,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1935,10 +1935,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133828540</v>
+        <v>133828530</v>
       </c>
       <c r="B14" t="n">
-        <v>83319</v>
+        <v>80453</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1946,21 +1946,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1970,13 +1970,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>514417</v>
+        <v>514326</v>
       </c>
       <c r="R14" t="n">
-        <v>6910549</v>
+        <v>6910602</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2005,7 +2005,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2015,7 +2015,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2042,10 +2042,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133828530</v>
+        <v>133828553</v>
       </c>
       <c r="B15" t="n">
-        <v>80439</v>
+        <v>57965</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2053,37 +2053,45 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Linnbäckrönningen, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>514326</v>
+        <v>514473</v>
       </c>
       <c r="R15" t="n">
-        <v>6910602</v>
+        <v>6910487</v>
       </c>
       <c r="S15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2112,7 +2120,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2122,7 +2130,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2152,7 +2165,7 @@
         <v>133828557</v>
       </c>
       <c r="B16" t="n">
-        <v>83319</v>
+        <v>83333</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2259,7 +2272,7 @@
         <v>133828533</v>
       </c>
       <c r="B17" t="n">
-        <v>83319</v>
+        <v>83333</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2363,10 +2376,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133828553</v>
+        <v>133828551</v>
       </c>
       <c r="B18" t="n">
-        <v>57958</v>
+        <v>83325</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2374,45 +2387,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Linnbäckrönningen, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>514473</v>
+        <v>514417</v>
       </c>
       <c r="R18" t="n">
-        <v>6910487</v>
+        <v>6910512</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2441,7 +2446,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2451,12 +2456,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:21</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2486,7 +2486,7 @@
         <v>133828539</v>
       </c>
       <c r="B19" t="n">
-        <v>83319</v>
+        <v>83333</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>133828558</v>
       </c>
       <c r="B20" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         <v>133828546</v>
       </c>
       <c r="B21" t="n">
-        <v>99140</v>
+        <v>99168</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>133828570</v>
       </c>
       <c r="B22" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>133828549</v>
       </c>
       <c r="B23" t="n">
-        <v>83302</v>
+        <v>83316</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>133828559</v>
       </c>
       <c r="B24" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>133828548</v>
       </c>
       <c r="B25" t="n">
-        <v>99140</v>
+        <v>99168</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3271,7 +3271,7 @@
         <v>133828556</v>
       </c>
       <c r="B26" t="n">
-        <v>83319</v>
+        <v>83333</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>133828542</v>
       </c>
       <c r="B27" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3498,7 +3498,7 @@
         <v>133828545</v>
       </c>
       <c r="B28" t="n">
-        <v>91928</v>
+        <v>91947</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         <v>133828544</v>
       </c>
       <c r="B29" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3709,10 +3709,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133828550</v>
+        <v>133828535</v>
       </c>
       <c r="B30" t="n">
-        <v>83319</v>
+        <v>57965</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3720,34 +3720,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Linnbäckrönningen, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>514408</v>
+        <v>514363</v>
       </c>
       <c r="R30" t="n">
-        <v>6910507</v>
+        <v>6910589</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3779,7 +3787,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3789,7 +3797,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3816,10 +3829,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133828535</v>
+        <v>133828552</v>
       </c>
       <c r="B31" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3859,10 +3872,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>514363</v>
+        <v>514420</v>
       </c>
       <c r="R31" t="n">
-        <v>6910589</v>
+        <v>6910512</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3894,7 +3907,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3904,7 +3917,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -3936,10 +3949,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133828552</v>
+        <v>133828550</v>
       </c>
       <c r="B32" t="n">
-        <v>57958</v>
+        <v>83333</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3947,42 +3960,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Linnbäckrönningen, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>514420</v>
+        <v>514408</v>
       </c>
       <c r="R32" t="n">
-        <v>6910512</v>
+        <v>6910507</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4014,7 +4019,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4024,12 +4029,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>17:17</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4059,7 +4059,7 @@
         <v>133828538</v>
       </c>
       <c r="B33" t="n">
-        <v>57955</v>
+        <v>57962</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4171,7 +4171,7 @@
         <v>133828531</v>
       </c>
       <c r="B34" t="n">
-        <v>79358</v>
+        <v>79372</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
         <v>133828536</v>
       </c>
       <c r="B35" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
         <v>133828537</v>
       </c>
       <c r="B36" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 46375-2025 artfynd.xlsx
+++ b/artfynd/A 46375-2025 artfynd.xlsx
@@ -1163,7 +1163,7 @@
         <v>133828543</v>
       </c>
       <c r="B7" t="n">
-        <v>83333</v>
+        <v>83343</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>133828532</v>
       </c>
       <c r="B8" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>133828569</v>
       </c>
       <c r="B9" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1497,7 +1497,7 @@
         <v>133828555</v>
       </c>
       <c r="B10" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1617,7 +1617,7 @@
         <v>133828560</v>
       </c>
       <c r="B11" t="n">
-        <v>83333</v>
+        <v>83343</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1724,7 +1724,7 @@
         <v>133828547</v>
       </c>
       <c r="B12" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         <v>133828540</v>
       </c>
       <c r="B13" t="n">
-        <v>83333</v>
+        <v>83343</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
         <v>133828530</v>
       </c>
       <c r="B14" t="n">
-        <v>80453</v>
+        <v>80473</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>133828553</v>
       </c>
       <c r="B15" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>133828557</v>
       </c>
       <c r="B16" t="n">
-        <v>83333</v>
+        <v>83343</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>133828533</v>
       </c>
       <c r="B17" t="n">
-        <v>83333</v>
+        <v>83343</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>133828551</v>
       </c>
       <c r="B18" t="n">
-        <v>83325</v>
+        <v>83335</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
         <v>133828539</v>
       </c>
       <c r="B19" t="n">
-        <v>83333</v>
+        <v>83343</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>133828558</v>
       </c>
       <c r="B20" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         <v>133828546</v>
       </c>
       <c r="B21" t="n">
-        <v>99168</v>
+        <v>99178</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>133828570</v>
       </c>
       <c r="B22" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>133828549</v>
       </c>
       <c r="B23" t="n">
-        <v>83316</v>
+        <v>83326</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>133828559</v>
       </c>
       <c r="B24" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>133828548</v>
       </c>
       <c r="B25" t="n">
-        <v>99168</v>
+        <v>99178</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3271,7 +3271,7 @@
         <v>133828556</v>
       </c>
       <c r="B26" t="n">
-        <v>83333</v>
+        <v>83343</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>133828542</v>
       </c>
       <c r="B27" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3498,7 +3498,7 @@
         <v>133828545</v>
       </c>
       <c r="B28" t="n">
-        <v>91947</v>
+        <v>91957</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         <v>133828544</v>
       </c>
       <c r="B29" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3709,10 +3709,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133828535</v>
+        <v>133828550</v>
       </c>
       <c r="B30" t="n">
-        <v>57965</v>
+        <v>83343</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3720,42 +3720,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Linnbäckrönningen, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>514363</v>
+        <v>514408</v>
       </c>
       <c r="R30" t="n">
-        <v>6910589</v>
+        <v>6910507</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3787,7 +3779,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3797,12 +3789,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:36</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3829,10 +3816,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133828552</v>
+        <v>133828535</v>
       </c>
       <c r="B31" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3872,10 +3859,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>514420</v>
+        <v>514363</v>
       </c>
       <c r="R31" t="n">
-        <v>6910512</v>
+        <v>6910589</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3907,7 +3894,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3917,7 +3904,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -3949,10 +3936,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133828550</v>
+        <v>133828552</v>
       </c>
       <c r="B32" t="n">
-        <v>83333</v>
+        <v>57975</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3960,34 +3947,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Linnbäckrönningen, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>514408</v>
+        <v>514420</v>
       </c>
       <c r="R32" t="n">
-        <v>6910507</v>
+        <v>6910512</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4019,7 +4014,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4029,7 +4024,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:17</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4059,7 +4059,7 @@
         <v>133828538</v>
       </c>
       <c r="B33" t="n">
-        <v>57962</v>
+        <v>57972</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4171,7 +4171,7 @@
         <v>133828531</v>
       </c>
       <c r="B34" t="n">
-        <v>79372</v>
+        <v>79382</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
         <v>133828536</v>
       </c>
       <c r="B35" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
         <v>133828537</v>
       </c>
       <c r="B36" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 46375-2025 artfynd.xlsx
+++ b/artfynd/A 46375-2025 artfynd.xlsx
@@ -2269,10 +2269,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133828533</v>
+        <v>133828551</v>
       </c>
       <c r="B17" t="n">
-        <v>83343</v>
+        <v>83335</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2280,21 +2280,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6440</v>
+        <v>308</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2304,13 +2304,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>514356</v>
+        <v>514417</v>
       </c>
       <c r="R17" t="n">
-        <v>6910600</v>
+        <v>6910512</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2339,7 +2339,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2376,10 +2376,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133828551</v>
+        <v>133828533</v>
       </c>
       <c r="B18" t="n">
-        <v>83335</v>
+        <v>83343</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2387,21 +2387,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>308</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2411,13 +2411,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>514417</v>
+        <v>514356</v>
       </c>
       <c r="R18" t="n">
-        <v>6910512</v>
+        <v>6910600</v>
       </c>
       <c r="S18" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3602,10 +3602,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133828544</v>
+        <v>133828535</v>
       </c>
       <c r="B29" t="n">
-        <v>79358</v>
+        <v>57975</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3613,34 +3613,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Linnbäckrönningen, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>514389</v>
+        <v>514363</v>
       </c>
       <c r="R29" t="n">
-        <v>6910544</v>
+        <v>6910589</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3672,7 +3680,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3682,7 +3690,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3709,10 +3722,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133828550</v>
+        <v>133828552</v>
       </c>
       <c r="B30" t="n">
-        <v>83343</v>
+        <v>57975</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3720,34 +3733,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Linnbäckrönningen, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>514408</v>
+        <v>514420</v>
       </c>
       <c r="R30" t="n">
-        <v>6910507</v>
+        <v>6910512</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3779,7 +3800,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3789,7 +3810,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:17</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3816,10 +3842,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133828535</v>
+        <v>133828544</v>
       </c>
       <c r="B31" t="n">
-        <v>57975</v>
+        <v>79358</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3827,42 +3853,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Linnbäckrönningen, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>514363</v>
+        <v>514389</v>
       </c>
       <c r="R31" t="n">
-        <v>6910589</v>
+        <v>6910544</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3894,7 +3912,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3904,12 +3922,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:36</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3936,10 +3949,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133828552</v>
+        <v>133828550</v>
       </c>
       <c r="B32" t="n">
-        <v>57975</v>
+        <v>83343</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3947,42 +3960,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Linnbäckrönningen, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>514420</v>
+        <v>514408</v>
       </c>
       <c r="R32" t="n">
-        <v>6910512</v>
+        <v>6910507</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4014,7 +4019,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4024,12 +4029,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>17:17</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 46375-2025 artfynd.xlsx
+++ b/artfynd/A 46375-2025 artfynd.xlsx
@@ -2269,10 +2269,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133828551</v>
+        <v>133828533</v>
       </c>
       <c r="B17" t="n">
-        <v>83335</v>
+        <v>83343</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2280,21 +2280,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>308</v>
+        <v>6440</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2304,13 +2304,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>514417</v>
+        <v>514356</v>
       </c>
       <c r="R17" t="n">
-        <v>6910512</v>
+        <v>6910600</v>
       </c>
       <c r="S17" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2339,7 +2339,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2376,10 +2376,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133828533</v>
+        <v>133828551</v>
       </c>
       <c r="B18" t="n">
-        <v>83343</v>
+        <v>83335</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2387,21 +2387,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6440</v>
+        <v>308</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2411,13 +2411,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>514356</v>
+        <v>514417</v>
       </c>
       <c r="R18" t="n">
-        <v>6910600</v>
+        <v>6910512</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3722,10 +3722,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133828552</v>
+        <v>133828544</v>
       </c>
       <c r="B30" t="n">
-        <v>57975</v>
+        <v>79358</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3733,42 +3733,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Linnbäckrönningen, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>514420</v>
+        <v>514389</v>
       </c>
       <c r="R30" t="n">
-        <v>6910512</v>
+        <v>6910544</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3800,7 +3792,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3810,12 +3802,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:17</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3842,10 +3829,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133828544</v>
+        <v>133828552</v>
       </c>
       <c r="B31" t="n">
-        <v>79358</v>
+        <v>57975</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3853,34 +3840,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Linnbäckrönningen, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>514389</v>
+        <v>514420</v>
       </c>
       <c r="R31" t="n">
-        <v>6910544</v>
+        <v>6910512</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3912,7 +3907,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3922,7 +3917,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:17</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 46375-2025 artfynd.xlsx
+++ b/artfynd/A 46375-2025 artfynd.xlsx
@@ -1163,7 +1163,7 @@
         <v>133828543</v>
       </c>
       <c r="B7" t="n">
-        <v>83343</v>
+        <v>83344</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>133828532</v>
       </c>
       <c r="B8" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1617,7 +1617,7 @@
         <v>133828560</v>
       </c>
       <c r="B11" t="n">
-        <v>83343</v>
+        <v>83344</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1724,7 +1724,7 @@
         <v>133828547</v>
       </c>
       <c r="B12" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         <v>133828540</v>
       </c>
       <c r="B13" t="n">
-        <v>83343</v>
+        <v>83344</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1935,10 +1935,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133828530</v>
+        <v>133828533</v>
       </c>
       <c r="B14" t="n">
-        <v>80473</v>
+        <v>83344</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1946,21 +1946,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1970,13 +1970,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>514326</v>
+        <v>514356</v>
       </c>
       <c r="R14" t="n">
-        <v>6910602</v>
+        <v>6910600</v>
       </c>
       <c r="S14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2005,7 +2005,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2015,7 +2015,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2042,10 +2042,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133828553</v>
+        <v>133828530</v>
       </c>
       <c r="B15" t="n">
-        <v>57975</v>
+        <v>80474</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2053,45 +2053,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Linnbäckrönningen, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>514473</v>
+        <v>514326</v>
       </c>
       <c r="R15" t="n">
-        <v>6910487</v>
+        <v>6910602</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2120,7 +2112,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2130,12 +2122,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:21</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2162,10 +2149,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133828557</v>
+        <v>133828553</v>
       </c>
       <c r="B16" t="n">
-        <v>83343</v>
+        <v>57975</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2173,24 +2160,32 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Linnbäckrönningen, Mpd</t>
@@ -2200,7 +2195,7 @@
         <v>514473</v>
       </c>
       <c r="R16" t="n">
-        <v>6910454</v>
+        <v>6910487</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2232,7 +2227,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2242,7 +2237,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2269,10 +2269,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133828533</v>
+        <v>133828557</v>
       </c>
       <c r="B17" t="n">
-        <v>83343</v>
+        <v>83344</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2304,10 +2304,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>514356</v>
+        <v>514473</v>
       </c>
       <c r="R17" t="n">
-        <v>6910600</v>
+        <v>6910454</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2339,7 +2339,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2379,7 +2379,7 @@
         <v>133828551</v>
       </c>
       <c r="B18" t="n">
-        <v>83335</v>
+        <v>83336</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
         <v>133828539</v>
       </c>
       <c r="B19" t="n">
-        <v>83343</v>
+        <v>83344</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         <v>133828546</v>
       </c>
       <c r="B21" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>133828570</v>
       </c>
       <c r="B22" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>133828549</v>
       </c>
       <c r="B23" t="n">
-        <v>83326</v>
+        <v>83327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>133828548</v>
       </c>
       <c r="B25" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3271,7 +3271,7 @@
         <v>133828556</v>
       </c>
       <c r="B26" t="n">
-        <v>83343</v>
+        <v>83344</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3498,7 +3498,7 @@
         <v>133828545</v>
       </c>
       <c r="B28" t="n">
-        <v>91957</v>
+        <v>91959</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3602,10 +3602,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133828535</v>
+        <v>133828544</v>
       </c>
       <c r="B29" t="n">
-        <v>57975</v>
+        <v>79359</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3613,42 +3613,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Linnbäckrönningen, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>514363</v>
+        <v>514389</v>
       </c>
       <c r="R29" t="n">
-        <v>6910589</v>
+        <v>6910544</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3680,7 +3672,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3690,12 +3682,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:36</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3722,10 +3709,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133828544</v>
+        <v>133828535</v>
       </c>
       <c r="B30" t="n">
-        <v>79358</v>
+        <v>57975</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3733,34 +3720,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Linnbäckrönningen, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>514389</v>
+        <v>514363</v>
       </c>
       <c r="R30" t="n">
-        <v>6910544</v>
+        <v>6910589</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3792,7 +3787,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3802,7 +3797,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3952,7 +3952,7 @@
         <v>133828550</v>
       </c>
       <c r="B32" t="n">
-        <v>83343</v>
+        <v>83344</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4171,7 +4171,7 @@
         <v>133828531</v>
       </c>
       <c r="B34" t="n">
-        <v>79382</v>
+        <v>79383</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
         <v>133828536</v>
       </c>
       <c r="B35" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
